--- a/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-patient-death-place.xlsx
+++ b/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-patient-death-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:00:17+00:00</t>
+    <t>2025-02-04T09:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-patient-death-place.xlsx
+++ b/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-patient-death-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:12:17+00:00</t>
+    <t>2025-02-04T10:05:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-patient-death-place.xlsx
+++ b/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-patient-death-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T10:05:16+00:00</t>
+    <t>2025-02-04T10:10:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-patient-death-place.xlsx
+++ b/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-patient-death-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T10:10:21+00:00</t>
+    <t>2025-02-04T14:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-patient-death-place.xlsx
+++ b/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-patient-death-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T14:40:03+00:00</t>
+    <t>2025-02-04T15:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
